--- a/Config/Excel/GameConfig/__tables__.xlsx
+++ b/Config/Excel/GameConfig/__tables__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="15320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24940" windowHeight="15320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="1"/>
@@ -1448,12 +1448,12 @@
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>SkillConfigCategory</t>
+          <t>EmitterUpgradeConfigCategory</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>SkillConfig</t>
+          <t>EmitterUpgradeConfig</t>
         </is>
       </c>
       <c r="D12" s="0" t="b">
@@ -1461,24 +1461,29 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>SkillConfig.xlsx</t>
+          <t>EmitterUpgradeConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>发射器升级配置</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>SkillConfigCategory</t>
+          <t>EmitterUpgradeConfigCategory</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>SkillTargetingConfigCategory</t>
+          <t>EmitterConfigCategory</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>SkillTargetingConfig</t>
+          <t>EmitterConfig</t>
         </is>
       </c>
       <c r="D13" s="0" t="b">
@@ -1486,24 +1491,24 @@
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>SkillTargetingConfig.xlsx</t>
+          <t>EmitterConfig.xlsx</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>SkillTargetingConfigCategory</t>
+          <t>EmitterConfigCategory</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>BuffGroupConfigCategory</t>
+          <t>SkillTargetingConfigCategory</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>BuffGroupConfig</t>
+          <t>SkillTargetingConfig</t>
         </is>
       </c>
       <c r="D14" s="0" t="b">
@@ -1511,24 +1516,24 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>BuffGroupConfig.xlsx</t>
+          <t>SkillTargetingConfig.xlsx</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t>BuffGroupConfigCategory</t>
+          <t>SkillTargetingConfigCategory</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>BuffConfigCategory</t>
+          <t>BuffGroupConfigCategory</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>BuffConfig</t>
+          <t>BuffGroupConfig</t>
         </is>
       </c>
       <c r="D15" s="0" t="b">
@@ -1536,24 +1541,24 @@
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>BuffConfig.xlsx</t>
+          <t>BuffGroupConfig.xlsx</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>BuffConfigCategory</t>
+          <t>BuffGroupConfigCategory</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>BattleGlobalConfigCategory</t>
+          <t>BuffConfigCategory</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>BattleGlobalConfig</t>
+          <t>BuffConfig</t>
         </is>
       </c>
       <c r="D16" s="0" t="b">
@@ -1561,17 +1566,112 @@
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
+          <t>BuffConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>BuffConfigCategory</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>BattleGlobalConfigCategory</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>BattleGlobalConfig</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
           <t>BattleGlobalConfig.xlsx</t>
         </is>
       </c>
-      <c r="G16" s="0" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="K16" s="0" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t>BattleGlobalConfigCategory</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customFormat="1" s="1">
+      <c r="A18"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EmitterEffectConfigCategory</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EmitterEffectConfig</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EmitterEffectConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>发射器效果配置</t>
+        </is>
+      </c>
+      <c r="J18"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>EmitterEffectConfigCategory</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="1" s="1">
+      <c r="A19"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EmitterEffectPackConfigCategory</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EmitterEffectPackConfig</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EmitterEffectPackConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>发射器效果包配置</t>
+        </is>
+      </c>
+      <c r="J19"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>EmitterEffectPackConfigCategory</t>
         </is>
       </c>
     </row>
